--- a/artfynd/A 15028-2026 artfynd.xlsx
+++ b/artfynd/A 15028-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4039066</v>
+        <v>6770794</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462991.611579031</v>
+        <v>462992</v>
       </c>
       <c r="R2" t="n">
-        <v>7041393.253265601</v>
+        <v>7041393</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1998-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1998-07-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,53 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>946393</v>
+        <v>6771170</v>
       </c>
       <c r="B3" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1968</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kåsbäcken, Bredbyn, Jmt</t>
+          <t>N BERGSFLON (19E8e14), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462918.6470925767</v>
+        <v>462962</v>
       </c>
       <c r="R3" t="n">
-        <v>7041503.534898484</v>
+        <v>7041390</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,27 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-08-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-09-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-09-02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Granskog med tallöverståndare ca 15-20%, blåbärsrismark, rikkärr omger objektet. Inga spår av brand, plockhugget, dåligt med död ved. Flesta naturvärden knutna till gran.</t>
+          <t>190484141 / CYPR CAL / Allmän-riklig (3)  / OBJ.AREA:0,9 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,97 +867,68 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Bodil Carlsson</t>
+          <t>Alf Pedersen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för hotade arter</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61260385</v>
+        <v>6771386</v>
       </c>
       <c r="B4" t="n">
-        <v>57073</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103056</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>TVA1, Jmt</t>
+          <t>Kåsbäcken, Bredbyn, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462751.7810321986</v>
+        <v>462929</v>
       </c>
       <c r="R4" t="n">
-        <v>7041538.533426915</v>
+        <v>7041595</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,25 +950,19 @@
           <t>Offerdal</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2009-08-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2009-08-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Granskog med tallöverståndare ca 15-20%, blåbärsrismark, rikkärr omger objektet. Inga spår av brand, plockhugget, dåligt med död ved. Flesta naturvärden knutna till gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,66 +973,70 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Bodil Carlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6771386</v>
+        <v>130021407</v>
       </c>
       <c r="B5" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kåsbäcken, Bredbyn, Jmt</t>
+          <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462929.1083870935</v>
+        <v>463294</v>
       </c>
       <c r="R5" t="n">
-        <v>7041595.423830352</v>
+        <v>7041644</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,27 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2009-08-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2009-08-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Granskog med tallöverståndare ca 15-20%, blåbärsrismark, rikkärr omger objektet. Inga spår av brand, plockhugget, dåligt med död ved. Flesta naturvärden knutna till gran.</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,84 +1079,61 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bodil Carlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Bodil Carlsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110156157</v>
+        <v>342872</v>
       </c>
       <c r="B6" t="n">
-        <v>98696</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>504</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2310</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sjöarbodarna / 700 m SSV /, myrdråg, Jmt</t>
+          <t>N BERGSFLON (19E8e14), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462992</v>
+        <v>462962</v>
       </c>
       <c r="R6" t="n">
-        <v>7041393</v>
+        <v>7041390</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1257,24 +1158,19 @@
           <t>Offerdal</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Z-Kro-1355</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
+          <t>1998-09-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
+          <t>1998-09-02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2310 skott, mestadels med blomma/blomknopp. En hel del hade inte kommit så långt i skuggigare delar av lokalen, så svårt att avgöra om det blir blommor eller inte på dessa skott. Annars väldigt fint område för guckuskon, i ängsartad mark intill barrskogskanten. OBS! Finns även Ö om skoterleden, om än betydligt färre.</t>
+          <t>190484141 / PHE FERF / Enstaka-sparsam (1)  / OBJ.AREA:0,9 ha</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,73 +1181,73 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Rikkärr/kalkkärr /</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Alf Pedersen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6771170</v>
+        <v>130021389</v>
       </c>
       <c r="B7" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>504</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N BERGSFLON (19E8e14), Jmt</t>
+          <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462962.0539211394</v>
+        <v>463160</v>
       </c>
       <c r="R7" t="n">
-        <v>7041390.0232072</v>
+        <v>7041553</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1375,27 +1271,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1998-09-02</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1998-09-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>190484141 / CYPR CAL / Allmän-riklig (3)  / OBJ.AREA:0,9 ha</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,26 +1291,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alf Pedersen</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130021083</v>
+        <v>946393</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>93231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,37 +1314,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1968</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sjöarbodarna, Jmt</t>
+          <t>Kåsbäcken, Bredbyn, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463194</v>
+        <v>462919</v>
       </c>
       <c r="R8" t="n">
-        <v>7041747</v>
+        <v>7041504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,12 +1368,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2009-08-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2009-08-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Granskog med tallöverståndare ca 15-20%, blåbärsrismark, rikkärr omger objektet. Inga spår av brand, plockhugget, dåligt med död ved. Flesta naturvärden knutna till gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,86 +1387,64 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Bodil Carlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130021074</v>
+        <v>130021080</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1595,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463102</v>
+        <v>463122</v>
       </c>
       <c r="R9" t="n">
-        <v>7041718</v>
+        <v>7041782</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1633,17 +1490,13 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1664,12 +1517,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1687,45 +1540,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130021396</v>
+        <v>130021081</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463184</v>
+        <v>463097</v>
       </c>
       <c r="R10" t="n">
-        <v>7041598</v>
+        <v>7041741</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,74 +1616,98 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130021407</v>
+        <v>130021082</v>
       </c>
       <c r="B11" t="n">
-        <v>91724</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463294</v>
+        <v>463145</v>
       </c>
       <c r="R11" t="n">
-        <v>7041644</v>
+        <v>7041721</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,38 +1742,69 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130021080</v>
+        <v>130021083</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1924,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463122</v>
+        <v>463194</v>
       </c>
       <c r="R12" t="n">
-        <v>7041782</v>
+        <v>7041747</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1974,7 +1885,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2012,45 +1923,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130021398</v>
+        <v>130021084</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463169</v>
+        <v>463194</v>
       </c>
       <c r="R13" t="n">
-        <v>7041613</v>
+        <v>7041782</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,7 +2001,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,63 +2010,92 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130021389</v>
+        <v>130021085</v>
       </c>
       <c r="B14" t="n">
-        <v>91728</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463160</v>
+        <v>463175</v>
       </c>
       <c r="R14" t="n">
-        <v>7041553</v>
+        <v>7041811</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2187,24 +2130,55 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en skadad gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2214,11 +2188,11 @@
         <v>130021086</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2342,41 +2316,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130021412</v>
+        <v>130021087</v>
       </c>
       <c r="B16" t="n">
-        <v>91748</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463279</v>
+        <v>463238</v>
       </c>
       <c r="R16" t="n">
-        <v>7041801</v>
+        <v>7041799</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2411,77 +2392,100 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130021075</v>
+        <v>130021413</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463139</v>
+        <v>463054</v>
       </c>
       <c r="R17" t="n">
-        <v>7041707</v>
+        <v>7041724</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2518,7 +2522,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, glest spridda längs ca 7 meter på en granstam.</t>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2529,71 +2533,50 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130021408</v>
+        <v>130021414</v>
       </c>
       <c r="B18" t="n">
-        <v>91748</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2601,10 +2584,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463236</v>
+        <v>463264</v>
       </c>
       <c r="R18" t="n">
-        <v>7041582</v>
+        <v>7041556</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,6 +2620,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,14 +2651,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130021414</v>
+        <v>130021415</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2698,10 +2686,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463264</v>
+        <v>463200</v>
       </c>
       <c r="R19" t="n">
-        <v>7041556</v>
+        <v>7041585</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2738,7 +2726,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ganska rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,10 +2753,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130021393</v>
+        <v>130021074</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2794,16 +2782,24 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463281</v>
+        <v>463102</v>
       </c>
       <c r="R20" t="n">
-        <v>7041580</v>
+        <v>7041718</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2840,7 +2836,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,26 +2847,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130021404</v>
+        <v>130021075</v>
       </c>
       <c r="B21" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,16 +2917,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463344</v>
+        <v>463139</v>
       </c>
       <c r="R21" t="n">
-        <v>7041755</v>
+        <v>7041707</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2942,7 +2971,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, glest spridda längs ca 7 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2953,26 +2982,51 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130021400</v>
+        <v>130021076</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2998,16 +3052,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463187</v>
+        <v>463133</v>
       </c>
       <c r="R22" t="n">
-        <v>7041519</v>
+        <v>7041708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3044,7 +3106,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre och några på gränsen till färska, i hyfsat riklig mängd längs minst 6 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3055,26 +3117,51 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130021084</v>
+        <v>130021390</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,37 +3169,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463194</v>
+        <v>463045</v>
       </c>
       <c r="R23" t="n">
-        <v>7041782</v>
+        <v>7041711</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,7 +3233,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,54 +3242,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130021402</v>
+        <v>130021391</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,10 +3295,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463201</v>
+        <v>463049</v>
       </c>
       <c r="R24" t="n">
-        <v>7041523</v>
+        <v>7041720</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3277,7 +3335,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3307,7 +3365,7 @@
         <v>130021392</v>
       </c>
       <c r="B25" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3406,10 +3464,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130021395</v>
+        <v>130021393</v>
       </c>
       <c r="B26" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3441,10 +3499,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>463188</v>
+        <v>463281</v>
       </c>
       <c r="R26" t="n">
-        <v>7041600</v>
+        <v>7041580</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3508,10 +3566,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130021410</v>
+        <v>130021394</v>
       </c>
       <c r="B27" t="n">
-        <v>91748</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3519,19 +3577,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3539,10 +3601,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463239</v>
+        <v>463192</v>
       </c>
       <c r="R27" t="n">
-        <v>7041515</v>
+        <v>7041600</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3575,6 +3637,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,10 +3668,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130021087</v>
+        <v>130021395</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3612,37 +3679,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463238</v>
+        <v>463188</v>
       </c>
       <c r="R28" t="n">
-        <v>7041799</v>
+        <v>7041600</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3679,7 +3743,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I riklig mängd på en stående död gran med full längd.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3688,93 +3752,63 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130021077</v>
+        <v>130021396</v>
       </c>
       <c r="B29" t="n">
-        <v>97791</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463145</v>
+        <v>463184</v>
       </c>
       <c r="R29" t="n">
-        <v>7041732</v>
+        <v>7041598</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3809,40 +3843,39 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130021399</v>
+        <v>130021397</v>
       </c>
       <c r="B30" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3874,10 +3907,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463172</v>
+        <v>463162</v>
       </c>
       <c r="R30" t="n">
-        <v>7041608</v>
+        <v>7041614</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3914,7 +3947,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,10 +3974,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130021401</v>
+        <v>130021398</v>
       </c>
       <c r="B31" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3976,10 +4009,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463196</v>
+        <v>463169</v>
       </c>
       <c r="R31" t="n">
-        <v>7041524</v>
+        <v>7041613</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4016,7 +4049,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4043,10 +4076,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130021391</v>
+        <v>130021399</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4078,10 +4111,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463049</v>
+        <v>463172</v>
       </c>
       <c r="R32" t="n">
-        <v>7041720</v>
+        <v>7041608</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4118,7 +4151,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,10 +4178,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130021076</v>
+        <v>130021400</v>
       </c>
       <c r="B33" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4174,24 +4207,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463133</v>
+        <v>463187</v>
       </c>
       <c r="R33" t="n">
-        <v>7041708</v>
+        <v>7041519</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4228,7 +4253,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och några på gränsen till färska, i hyfsat riklig mängd längs minst 6 meter på en granstam.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,51 +4264,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130021413</v>
+        <v>130021401</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463054</v>
+        <v>463196</v>
       </c>
       <c r="R34" t="n">
-        <v>7041724</v>
+        <v>7041524</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ganska rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4382,10 +4382,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130021403</v>
+        <v>130021402</v>
       </c>
       <c r="B35" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463229</v>
+        <v>463201</v>
       </c>
       <c r="R35" t="n">
-        <v>7041515</v>
+        <v>7041523</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4484,10 +4484,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130021415</v>
+        <v>130021403</v>
       </c>
       <c r="B36" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,21 +4495,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463200</v>
+        <v>463229</v>
       </c>
       <c r="R36" t="n">
-        <v>7041585</v>
+        <v>7041515</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4586,10 +4586,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130021390</v>
+        <v>130021404</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463045</v>
+        <v>463344</v>
       </c>
       <c r="R37" t="n">
-        <v>7041711</v>
+        <v>7041755</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130021081</v>
+        <v>130021405</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4699,37 +4699,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463097</v>
+        <v>463374</v>
       </c>
       <c r="R38" t="n">
-        <v>7041741</v>
+        <v>7041740</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4764,60 +4761,39 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130021405</v>
+        <v>130021406</v>
       </c>
       <c r="B39" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4849,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463374</v>
+        <v>463384</v>
       </c>
       <c r="R39" t="n">
-        <v>7041740</v>
+        <v>7041759</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4889,7 +4865,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4916,10 +4892,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130021394</v>
+        <v>62189380</v>
       </c>
       <c r="B40" t="n">
-        <v>57826</v>
+        <v>58057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4927,16 +4903,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4947,14 +4923,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sjöarbodarna, Jmt</t>
+          <t>Kåsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463192</v>
+        <v>462981</v>
       </c>
       <c r="R40" t="n">
-        <v>7041600</v>
+        <v>7041347</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4981,17 +4957,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2005-09-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2005-09-15</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Kåsbäcken, 2,5 km SÖ om Bredbyn, 300 m Ö om Tvåtjärnarna.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5002,60 +4978,92 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Litet rikkärr delvis omgivet av äldre granskog.</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Hanna Wallén</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130021411</v>
+        <v>61260385</v>
       </c>
       <c r="B41" t="n">
-        <v>91748</v>
+        <v>58656</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>103056</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sjöarbodarna, Jmt</t>
+          <t>TVA1, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>463339</v>
+        <v>462752</v>
       </c>
       <c r="R41" t="n">
-        <v>7041763</v>
+        <v>7041539</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5077,14 +5085,25 @@
           <t>Offerdal</t>
         </is>
       </c>
+      <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2016-05-17</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2016-05-17</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5099,56 +5118,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130021409</v>
+        <v>2452299</v>
       </c>
       <c r="B42" t="n">
-        <v>91748</v>
+        <v>99022</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>220093</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sjöarbodarna, Jmt</t>
+          <t>N BERGSFLON (19E8e14), Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>463216</v>
+        <v>462962</v>
       </c>
       <c r="R42" t="n">
-        <v>7041521</v>
+        <v>7041390</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5172,12 +5195,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>1998-09-02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>1998-09-02</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>190484141 / CORA TRI / Tämligen allmän (2)  / OBJ.AREA:0,9 ha</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,64 +5216,73 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Rikkärr/kalkkärr /</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Alf Pedersen</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130021397</v>
+        <v>4039066</v>
       </c>
       <c r="B43" t="n">
-        <v>57826</v>
+        <v>106229</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sjöarbodarna, Jmt</t>
+          <t>LITET KÄRR 2,5 KM SSO BREDBYN, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463162</v>
+        <v>462992</v>
       </c>
       <c r="R43" t="n">
-        <v>7041614</v>
+        <v>7041393</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5269,17 +5306,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>1998-07-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>1998-07-01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>19E8E12 (Nystrand, P-O (2004): Rikkärr i Jämtlands kambrosilurområde, lst Z län)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5294,22 +5331,26 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Per-Olof Nystrand</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Per-olof Nystrand</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Våtmarksinventeringen Z-län (Rikkärrsinventering)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130021078</v>
+        <v>130021077</v>
       </c>
       <c r="B44" t="n">
-        <v>97791</v>
+        <v>97983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5345,10 +5386,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>463220</v>
+        <v>463145</v>
       </c>
       <c r="R44" t="n">
-        <v>7041764</v>
+        <v>7041732</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5413,37 +5454,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130021082</v>
+        <v>130021078</v>
       </c>
       <c r="B45" t="n">
-        <v>79180</v>
+        <v>97983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5451,10 +5493,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>463145</v>
+        <v>463220</v>
       </c>
       <c r="R45" t="n">
-        <v>7041721</v>
+        <v>7041764</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5489,11 +5531,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5509,26 +5546,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
@@ -5541,239 +5558,6 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>130021085</v>
-      </c>
-      <c r="B46" t="n">
-        <v>79180</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Sjöarbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>463175</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7041811</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På en skadad gran.</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>130021406</v>
-      </c>
-      <c r="B47" t="n">
-        <v>57826</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Sjöarbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>463384</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7041759</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15028-2026 artfynd.xlsx
+++ b/artfynd/A 15028-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Våtmarksinventeringen Z-län (Rikkärrsinventering)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6770794</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6771170</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6771386</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021407</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,6 +1228,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/342872</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021389</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/946393</t>
         </is>
       </c>
     </row>
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021080</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1663,6 +1708,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021081</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021082</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1920,6 +1975,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021083</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2051,6 +2111,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021084</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2182,6 +2247,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021085</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2313,6 +2383,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021086</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2444,6 +2519,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021087</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2546,6 +2626,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021413</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2648,6 +2733,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021414</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2750,6 +2840,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021415</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2885,6 +2980,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021074</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3020,6 +3120,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021075</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3155,6 +3260,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021076</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3257,6 +3367,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021390</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3359,6 +3474,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021391</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3461,6 +3581,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021392</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3563,6 +3688,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021393</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3665,6 +3795,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021394</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3767,6 +3902,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021395</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3869,6 +4009,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021396</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3971,6 +4116,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021397</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4073,6 +4223,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021398</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4175,6 +4330,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021399</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4277,6 +4437,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021400</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4379,6 +4544,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021401</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4481,6 +4651,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021402</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4583,6 +4758,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021403</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4685,6 +4865,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021404</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4787,6 +4972,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021405</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4889,6 +5079,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021406</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5000,6 +5195,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62189380</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5127,6 +5327,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61260385</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5238,6 +5443,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2452299</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5342,6 +5552,11 @@
       <c r="AY43" t="inlineStr">
         <is>
           <t>Våtmarksinventeringen Z-län (Rikkärrsinventering)</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4039066</t>
         </is>
       </c>
     </row>
@@ -5451,6 +5666,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021077</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5558,8 +5778,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021078</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>